--- a/data/pupil/3_processed/15_semantic_similarity/event/sub_1026_cosine_similarity.xlsx
+++ b/data/pupil/3_processed/15_semantic_similarity/event/sub_1026_cosine_similarity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,6 +456,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Impatient Billionaire</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Dont Look</t>
         </is>
       </c>
@@ -477,6 +482,9 @@
         <v>0.4456720054149628</v>
       </c>
       <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.1376163810491562</v>
       </c>
     </row>
@@ -499,6 +507,9 @@
       <c r="F3" t="n">
         <v>0</v>
       </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,6 +530,9 @@
       <c r="F4" t="n">
         <v>0</v>
       </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -539,6 +553,9 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,6 +574,9 @@
         <v>0.4543510377407074</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.2295985817909241</v>
       </c>
     </row>
@@ -577,6 +597,9 @@
         <v>0.8083198070526123</v>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.2029390037059784</v>
       </c>
     </row>
@@ -597,6 +620,9 @@
         <v>0.5585684180259705</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.1569462716579437</v>
       </c>
     </row>
@@ -617,6 +643,9 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>0.0325702503323555</v>
       </c>
     </row>
@@ -637,6 +666,9 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>0.5164997577667236</v>
       </c>
     </row>
@@ -657,6 +689,9 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.09558717906475067</v>
       </c>
     </row>
@@ -677,6 +712,9 @@
         <v>0.6182330250740051</v>
       </c>
       <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>0.205094575881958</v>
       </c>
     </row>
@@ -697,6 +735,9 @@
         <v>0.5599870085716248</v>
       </c>
       <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
         <v>0.065171018242836</v>
       </c>
     </row>
@@ -717,6 +758,9 @@
         <v>0.7578438520431519</v>
       </c>
       <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.09768485277891159</v>
       </c>
     </row>
@@ -737,6 +781,9 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.3080626130104065</v>
       </c>
     </row>
@@ -757,6 +804,9 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.1271148920059204</v>
       </c>
     </row>
@@ -777,6 +827,9 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.4669110774993896</v>
       </c>
     </row>
@@ -797,6 +850,9 @@
         <v>0.3427380919456482</v>
       </c>
       <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.319077730178833</v>
       </c>
     </row>
@@ -816,7 +872,8 @@
       <c r="E19" t="n">
         <v>0.4488710165023804</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
         <v>0.1666403114795685</v>
       </c>
     </row>
@@ -836,7 +893,8 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -856,7 +914,8 @@
       <c r="E21" t="n">
         <v>0.258516252040863</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
         <v>0.4716932773590088</v>
       </c>
     </row>
@@ -874,7 +933,8 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -892,7 +952,8 @@
       <c r="E23" t="n">
         <v>0.3457373380661011</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -910,7 +971,8 @@
       <c r="E24" t="n">
         <v>0.7404904961585999</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -926,7 +988,8 @@
       <c r="E25" t="n">
         <v>0.6925119757652283</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -942,7 +1005,8 @@
       <c r="E26" t="n">
         <v>0.5875480771064758</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -958,7 +1022,8 @@
       <c r="E27" t="n">
         <v>0.3222665190696716</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -974,7 +1039,8 @@
       <c r="E28" t="n">
         <v>0.4994087219238281</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
         <v>0.1217718124389648</v>
       </c>
     </row>
@@ -990,7 +1056,8 @@
       <c r="E29" t="n">
         <v>0.08119367808103561</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
         <v>0.3988727629184723</v>
       </c>
     </row>
@@ -1006,7 +1073,8 @@
       <c r="E30" t="n">
         <v>0.1557187885046005</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
         <v>0.3234495520591736</v>
       </c>
     </row>
@@ -1020,7 +1088,8 @@
         <v>0</v>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="n">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1034,7 +1103,8 @@
         <v>0</v>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1048,7 +1118,8 @@
         <v>0</v>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1062,7 +1133,8 @@
         <v>0</v>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="n">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1076,7 +1148,8 @@
         <v>0</v>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="n">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
         <v>0.5777815580368042</v>
       </c>
     </row>
@@ -1090,7 +1163,8 @@
         <v>0.5295205116271973</v>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="n">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
         <v>0.4400427043437958</v>
       </c>
     </row>
@@ -1104,7 +1178,8 @@
         <v>0.4566252827644348</v>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="n">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1118,7 +1193,8 @@
         <v>0</v>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="n">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1132,7 +1208,8 @@
         <v>0.1247349753975868</v>
       </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1146,7 +1223,8 @@
         <v>0.3505148589611053</v>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="n">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1160,7 +1238,8 @@
         <v>0.5045769810676575</v>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1174,7 +1253,8 @@
         <v>0.3090006411075592</v>
       </c>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="n">
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1189,6 +1269,7 @@
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1201,6 +1282,7 @@
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1213,6 +1295,7 @@
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1225,6 +1308,7 @@
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1237,6 +1321,7 @@
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1249,6 +1334,7 @@
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1261,6 +1347,7 @@
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1273,6 +1360,7 @@
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1285,6 +1373,7 @@
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1297,6 +1386,7 @@
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1309,6 +1399,7 @@
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1321,6 +1412,7 @@
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1333,6 +1425,7 @@
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1345,6 +1438,7 @@
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
